--- a/generated/sources/reports/apac/japan/【週次速報】国内店舗_2026年10月第3週(10.11-10.17).xlsx
+++ b/generated/sources/reports/apac/japan/【週次速報】国内店舗_2026年10月第3週(10.11-10.17).xlsx
@@ -73,55 +73,55 @@
     <t>販売点数TOP10（3店舗計）</t>
   </si>
   <si>
-    <t>MAYA black</t>
-  </si>
-  <si>
-    <t>MAYA navy</t>
-  </si>
-  <si>
-    <t>TRICOT PADDED CARDIGAN black</t>
-  </si>
-  <si>
-    <t>LOGO CARDIGAN black</t>
-  </si>
-  <si>
-    <t>HERMINE black</t>
-  </si>
-  <si>
-    <t>LOGO BEANIE black</t>
-  </si>
-  <si>
-    <t>KARAKORUM black</t>
-  </si>
-  <si>
-    <t>LOGO HOODIE navy</t>
-  </si>
-  <si>
-    <t>TRAILGRIP GTX black</t>
-  </si>
-  <si>
-    <t>BADY black</t>
+    <t>NOVA black</t>
+  </si>
+  <si>
+    <t>NOVA navy</t>
+  </si>
+  <si>
+    <t>VLOGO PADDED CARDIGAN black</t>
+  </si>
+  <si>
+    <t>VLOGO CARDIGAN black</t>
+  </si>
+  <si>
+    <t>LIVIANA black</t>
+  </si>
+  <si>
+    <t>VLOGO BEANIE black</t>
+  </si>
+  <si>
+    <t>COSIMO black</t>
+  </si>
+  <si>
+    <t>VLOGO HOODIE navy</t>
+  </si>
+  <si>
+    <t>VTRACK GTX black</t>
+  </si>
+  <si>
+    <t>ARIA black</t>
   </si>
   <si>
     <t>所感</t>
   </si>
   <si>
-    <t>・10/9の価格改定告知以降、MAYA・MAIRE・HERMINEを中心に駆け込み購入が本格化。銀座は前年比189%。</t>
+    <t>・10/9の価格改定告知以降、NOVA・AUREA・LIVIANAを中心に駆け込み購入が本格化。銀座は前年比189%。</t>
   </si>
   <si>
     <t>・10/12以降気温が下がり、ようやくダウンが動き始めた。</t>
   </si>
   <si>
-    <t>・ILVARO パウダーピンクは全店完売継続。10/8入荷分も即日完売。お取り置き・入荷待ちリスト：銀座8名、表参道6名、心斎橋7名（概数）。</t>
-  </si>
-  <si>
-    <t>・ブラック・オフホワイトのILVAROも問い合わせ増、サイズ1・2が欠品。</t>
-  </si>
-  <si>
-    <t>・TIBのファスナー不良返品は継続（交換対応）。</t>
-  </si>
-  <si>
-    <t>・価格改定前の在庫が不足する見込み。MAYAブラック サイズ3・4の追加配分を要請中。</t>
+    <t>・IRIDIA パウダーピンクは全店完売継続。10/8入荷分も即日完売。お取り置き・入荷待ちリスト：銀座8名、表参道6名、心斎橋7名（概数）。</t>
+  </si>
+  <si>
+    <t>・ブラック・オフホワイトのIRIDIAも問い合わせ増、サイズ1・2が欠品。</t>
+  </si>
+  <si>
+    <t>・VELのファスナー不良返品は継続（交換対応）。</t>
+  </si>
+  <si>
+    <t>・価格改定前の在庫が不足する見込み。NOVAブラック サイズ3・4の追加配分を要請中。</t>
   </si>
   <si>
     <t>社外秘　速報値のため確定値と異なる場合があります</t>
